--- a/public/downloads/StricklerSystematic2019.xlsx
+++ b/public/downloads/StricklerSystematic2019.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,13 +169,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>OOH</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
+    <t>O</t>
   </si>
   <si>
     <t>OH</t>
   </si>
   <si>
-    <t>O</t>
+    <t>OOH</t>
   </si>
 </sst>
 </file>
@@ -659,10 +682,10 @@
         <v>27</v>
       </c>
       <c r="N3" s="5">
-        <v>163.5381915569305</v>
+        <v>163538.1915569305</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03216090296104829</v>
+        <v>32.16090296104829</v>
       </c>
       <c r="P3" s="5">
         <v>5085</v>
@@ -709,10 +732,10 @@
         <v>27</v>
       </c>
       <c r="N4" s="5">
-        <v>172.0248911380768</v>
+        <v>172024.8911380768</v>
       </c>
       <c r="O4" s="4">
-        <v>0.06067897394641156</v>
+        <v>60.67897394641157</v>
       </c>
       <c r="P4" s="5">
         <v>2835</v>
@@ -759,10 +782,10 @@
         <v>27</v>
       </c>
       <c r="N5" s="5">
-        <v>434.0596508979797</v>
+        <v>434059.6508979797</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1494695767555027</v>
+        <v>149.4695767555027</v>
       </c>
       <c r="P5" s="5">
         <v>2904</v>
@@ -809,10 +832,10 @@
         <v>27</v>
       </c>
       <c r="N6" s="5">
-        <v>269.6554493904114</v>
+        <v>269655.4493904114</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08198706275172131</v>
+        <v>81.98706275172131</v>
       </c>
       <c r="P6" s="5">
         <v>3289</v>
@@ -859,10 +882,10 @@
         <v>27</v>
       </c>
       <c r="N7" s="5">
-        <v>777.0695695877075</v>
+        <v>777069.5695877075</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2714179425734221</v>
+        <v>271.4179425734221</v>
       </c>
       <c r="P7" s="5">
         <v>2863</v>
@@ -909,10 +932,10 @@
         <v>27</v>
       </c>
       <c r="N8" s="5">
-        <v>68.26777219772339</v>
+        <v>68267.77219772339</v>
       </c>
       <c r="O8" s="4">
-        <v>0.02083875830211337</v>
+        <v>20.83875830211337</v>
       </c>
       <c r="P8" s="5">
         <v>3276</v>
@@ -959,10 +982,10 @@
         <v>27</v>
       </c>
       <c r="N9" s="5">
-        <v>154.0990853309631</v>
+        <v>154099.0853309631</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03189136699730197</v>
+        <v>31.89136699730198</v>
       </c>
       <c r="P9" s="5">
         <v>4832</v>
@@ -1009,10 +1032,10 @@
         <v>27</v>
       </c>
       <c r="N10" s="5">
-        <v>278.3869826793671</v>
+        <v>278386.9826793671</v>
       </c>
       <c r="O10" s="4">
-        <v>0.09029743194270745</v>
+        <v>90.29743194270745</v>
       </c>
       <c r="P10" s="5">
         <v>3083</v>
@@ -1059,10 +1082,10 @@
         <v>27</v>
       </c>
       <c r="N11" s="5">
-        <v>136.5019690990448</v>
+        <v>136501.9690990448</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04180764750353592</v>
+        <v>41.80764750353593</v>
       </c>
       <c r="P11" s="5">
         <v>3265</v>
@@ -1109,10 +1132,10 @@
         <v>27</v>
       </c>
       <c r="N12" s="5">
-        <v>64.3897864818573</v>
+        <v>64389.7864818573</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02217279148824287</v>
+        <v>22.17279148824287</v>
       </c>
       <c r="P12" s="5">
         <v>2904</v>
@@ -1159,10 +1182,10 @@
         <v>27</v>
       </c>
       <c r="N13" s="5">
-        <v>228.1321830749512</v>
+        <v>228132.1830749512</v>
       </c>
       <c r="O13" s="4">
-        <v>0.0731427326306352</v>
+        <v>73.14273263063519</v>
       </c>
       <c r="P13" s="5">
         <v>3119</v>
@@ -1209,10 +1232,10 @@
         <v>27</v>
       </c>
       <c r="N14" s="5">
-        <v>1640.386281013489</v>
+        <v>1640386.281013489</v>
       </c>
       <c r="O14" s="4">
-        <v>0.3825527707587427</v>
+        <v>382.5527707587427</v>
       </c>
       <c r="P14" s="5">
         <v>4288</v>
@@ -1259,10 +1282,10 @@
         <v>27</v>
       </c>
       <c r="N15" s="5">
-        <v>1027.835741043091</v>
+        <v>1027835.741043091</v>
       </c>
       <c r="O15" s="4">
-        <v>0.384094073633442</v>
+        <v>384.094073633442</v>
       </c>
       <c r="P15" s="5">
         <v>2676</v>
@@ -1309,10 +1332,10 @@
         <v>27</v>
       </c>
       <c r="N16" s="5">
-        <v>442.4805476665497</v>
+        <v>442480.5476665497</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09739831557705254</v>
+        <v>97.39831557705254</v>
       </c>
       <c r="P16" s="5">
         <v>4543</v>
@@ -1359,10 +1382,10 @@
         <v>27</v>
       </c>
       <c r="N17" s="5">
-        <v>334.808988571167</v>
+        <v>334808.988571167</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1099175930962465</v>
+        <v>109.9175930962465</v>
       </c>
       <c r="P17" s="5">
         <v>3046</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,117 +1497,171 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2273622351306363</v>
+        <v>0.1268912376074073</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1172556783613998</v>
+        <v>0.1268912376074073</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1175893620460348</v>
+        <v>0.1340499779393566</v>
       </c>
       <c r="E3" s="4">
-        <v>89.84882842025706</v>
+        <v>90.74829931972791</v>
       </c>
       <c r="F3" s="4">
-        <v>84.207059408399</v>
+        <v>92.93810589112603</v>
       </c>
       <c r="G3" s="5">
         <v>9</v>
       </c>
       <c r="H3" s="5">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.02767693321305506</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1385027081976591</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1385027081976591</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1045662778540031</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1045662778540031</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.110195973831047</v>
+      </c>
+      <c r="E4" s="4">
+        <v>89.96598639455783</v>
+      </c>
+      <c r="F4" s="4">
+        <v>91.24161073825503</v>
+      </c>
+      <c r="G4" s="5">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.02866245880255727</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09009580248066275</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09009580248066275</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.2869011269167672</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3958076271642561</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.4099148036313388</v>
+      </c>
+      <c r="E5" s="4">
+        <v>87.65306122448979</v>
+      </c>
+      <c r="F5" s="4">
+        <v>80.99179716629301</v>
+      </c>
+      <c r="G5" s="5">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5">
         <v>6</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I5" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.07097540345821862</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.07097540345821862</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.0667091613092025</v>
-      </c>
-      <c r="E4" s="4">
-        <v>92.46031746031746</v>
-      </c>
-      <c r="F4" s="4">
-        <v>93.09843400447429</v>
-      </c>
-      <c r="G4" s="5">
-        <v>9</v>
-      </c>
-      <c r="H4" s="5">
-        <v>9</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.1604706155400122</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1604706155400122</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1477875026102351</v>
-      </c>
-      <c r="E5" s="4">
-        <v>93.4013605442177</v>
-      </c>
-      <c r="F5" s="4">
-        <v>94.51528709917972</v>
-      </c>
-      <c r="G5" s="5">
-        <v>9</v>
-      </c>
-      <c r="H5" s="5">
-        <v>9</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
       <c r="J5" s="5">
         <v>0</v>
       </c>
@@ -1583,9 +1674,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3958076271642561</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2428169947569749</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1633246021505066</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,132 +1797,202 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3770308523418559</v>
+        <v>0.8427295224241662</v>
       </c>
       <c r="C3" s="4">
-        <v>0.343313317654804</v>
+        <v>0.8438506978495089</v>
       </c>
       <c r="D3" s="4">
-        <v>0.328310165622434</v>
+        <v>0.8353702296520851</v>
       </c>
       <c r="E3" s="4">
-        <v>88.13303099017386</v>
+        <v>85.72562358276656</v>
       </c>
       <c r="F3" s="4">
-        <v>80.90231170768189</v>
+        <v>77.05567984091236</v>
       </c>
       <c r="G3" s="5">
         <v>9</v>
       </c>
       <c r="H3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.8438506978495089</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2764918751996516</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2157978903038168</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.544133008611987</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.4781785377112686</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.4465272941050102</v>
+      </c>
+      <c r="E4" s="4">
+        <v>86.21315192743772</v>
+      </c>
+      <c r="F4" s="4">
+        <v>78.85657469549918</v>
+      </c>
+      <c r="G4" s="5">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5">
+        <v>7</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.4768238995770194</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.239180293923613</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2223318758482218</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.6935340088896536</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.8824905512677219</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.7020366219949842</v>
+      </c>
+      <c r="E5" s="4">
+        <v>83.22373393801965</v>
+      </c>
+      <c r="F5" s="4">
+        <v>69.51528709917886</v>
+      </c>
+      <c r="G5" s="5">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5">
         <v>4</v>
       </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.1319661238237776</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1319661238237776</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.142196029270148</v>
-      </c>
-      <c r="E4" s="4">
-        <v>91.42857142857143</v>
-      </c>
-      <c r="F4" s="4">
-        <v>91.52870991797168</v>
-      </c>
-      <c r="G4" s="5">
-        <v>9</v>
-      </c>
-      <c r="H4" s="5">
-        <v>9</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.2896281417580692</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2896281417580692</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.284376363261433</v>
-      </c>
-      <c r="E5" s="4">
-        <v>93.85487528344672</v>
-      </c>
-      <c r="F5" s="4">
-        <v>95.45488441461596</v>
-      </c>
-      <c r="G5" s="5">
-        <v>9</v>
-      </c>
-      <c r="H5" s="5">
-        <v>9</v>
-      </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6935340088896536</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.8824905512677219</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2003,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2011,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2022,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2064,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,34 +2095,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3557136599248578</v>
+        <v>0.1604706155400122</v>
       </c>
       <c r="C3" s="4">
-        <v>0.07572619667920436</v>
+        <v>0.1604706155400122</v>
       </c>
       <c r="D3" s="4">
-        <v>0.132539276245388</v>
+        <v>0.1477875026102351</v>
       </c>
       <c r="E3" s="4">
-        <v>89.90551776266064</v>
+        <v>93.4013605442177</v>
       </c>
       <c r="F3" s="4">
-        <v>82.10290827740599</v>
+        <v>94.51528709917972</v>
       </c>
       <c r="G3" s="5">
         <v>9</v>
       </c>
       <c r="H3" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -1927,25 +2154,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.0763233270868966</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1180687671584029</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1180687671584029</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.08321084739693181</v>
+        <v>0.07097540345821862</v>
       </c>
       <c r="C4" s="4">
-        <v>0.08321084739693181</v>
+        <v>0.07097540345821862</v>
       </c>
       <c r="D4" s="4">
-        <v>0.07094288695449474</v>
+        <v>0.0667091613092025</v>
       </c>
       <c r="E4" s="4">
-        <v>92.57369614512471</v>
+        <v>92.46031746031746</v>
       </c>
       <c r="F4" s="4">
-        <v>92.42977877206079</v>
+        <v>93.09843400447429</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
@@ -1968,34 +2213,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.02203195490626738</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.07152171148669884</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07152171148669884</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.155381557044532</v>
+        <v>0.2273622351306363</v>
       </c>
       <c r="C5" s="4">
-        <v>0.155381557044532</v>
+        <v>0.1172556783613998</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1515474684011401</v>
+        <v>0.1175893620460348</v>
       </c>
       <c r="E5" s="4">
-        <v>94.01738473167045</v>
+        <v>89.84882842025706</v>
       </c>
       <c r="F5" s="4">
-        <v>95.40641312453394</v>
+        <v>84.207059408399</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2009,9 +2272,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1172556783613998</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2283066057827644</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06004439515889202</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2303,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2311,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2322,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2364,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,132 +2395,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4343963474723296</v>
+        <v>0.2896281417580692</v>
       </c>
       <c r="C3" s="4">
-        <v>0.04716358142579224</v>
+        <v>0.2896281417580692</v>
       </c>
       <c r="D3" s="4">
-        <v>0.09912568829013758</v>
+        <v>0.284376363261433</v>
       </c>
       <c r="E3" s="4">
-        <v>89.27815570672709</v>
+        <v>93.85487528344672</v>
       </c>
       <c r="F3" s="4">
-        <v>76.51752423564376</v>
+        <v>95.45488441461596</v>
       </c>
       <c r="G3" s="5">
         <v>9</v>
       </c>
       <c r="H3" s="5">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.2896281417580692</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08694453914351589</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08694453914351589</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1319661238237776</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1319661238237776</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.142196029270148</v>
+      </c>
+      <c r="E4" s="4">
+        <v>91.42857142857143</v>
+      </c>
+      <c r="F4" s="4">
+        <v>91.52870991797168</v>
+      </c>
+      <c r="G4" s="5">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.1070899418185655</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.08057975965470526</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08057975965470526</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3770308523418559</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.343313317654804</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.328310165622434</v>
+      </c>
+      <c r="E5" s="4">
+        <v>88.13303099017386</v>
+      </c>
+      <c r="F5" s="4">
+        <v>80.90231170768189</v>
+      </c>
+      <c r="G5" s="5">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5">
+        <v>5</v>
+      </c>
+      <c r="I5" s="5">
         <v>4</v>
       </c>
-      <c r="I3" s="5">
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.343313317654804</v>
+      </c>
+      <c r="O5" s="5">
         <v>5</v>
       </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.1436969746422076</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1436969746422076</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1398834402835531</v>
-      </c>
-      <c r="E4" s="4">
-        <v>93.86621315192744</v>
-      </c>
-      <c r="F4" s="4">
-        <v>94.22073079791204</v>
-      </c>
-      <c r="G4" s="5">
-        <v>9</v>
-      </c>
-      <c r="H4" s="5">
-        <v>9</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.07499470573974223</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.07499470573974223</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.07084213824503473</v>
-      </c>
-      <c r="E5" s="4">
-        <v>95.10204081632654</v>
-      </c>
-      <c r="F5" s="4">
-        <v>96.11856823266218</v>
-      </c>
-      <c r="G5" s="5">
-        <v>9</v>
-      </c>
-      <c r="H5" s="5">
-        <v>9</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
+      <c r="P5" s="4">
+        <v>0.4001283200572882</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.110238105418739</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2603,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2611,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2622,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2664,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,132 +2695,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3220436352762117</v>
+        <v>0.155381557044532</v>
       </c>
       <c r="C3" s="4">
-        <v>0.347881024661531</v>
+        <v>0.155381557044532</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3781973195366738</v>
+        <v>0.1515474684011401</v>
       </c>
       <c r="E3" s="4">
-        <v>76.20559334845048</v>
+        <v>94.01738473167045</v>
       </c>
       <c r="F3" s="4">
-        <v>70.09694258016421</v>
+        <v>95.40641312453394</v>
       </c>
       <c r="G3" s="5">
         <v>9</v>
       </c>
       <c r="H3" s="5">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.05891737040932791</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1246498966145787</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1246498966145787</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.08321084739693181</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.08321084739693181</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.07094288695449474</v>
+      </c>
+      <c r="E4" s="4">
+        <v>92.57369614512471</v>
+      </c>
+      <c r="F4" s="4">
+        <v>92.42977877206079</v>
+      </c>
+      <c r="G4" s="5">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.05876249890951613</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.07398530822917514</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07398530822917514</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3557136599248578</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.07572619667920436</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.132539276245388</v>
+      </c>
+      <c r="E5" s="4">
+        <v>89.90551776266064</v>
+      </c>
+      <c r="F5" s="4">
+        <v>82.10290827740599</v>
+      </c>
+      <c r="G5" s="5">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5">
         <v>5</v>
       </c>
-      <c r="I3" s="5">
-        <v>3</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2517285636580494</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2660651667739302</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3010581408788286</v>
-      </c>
-      <c r="E4" s="4">
-        <v>77.79667422524565</v>
-      </c>
-      <c r="F4" s="4">
-        <v>76.1558538404184</v>
-      </c>
-      <c r="G4" s="5">
-        <v>9</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="I5" s="5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.01208507070847418</v>
+      </c>
+      <c r="O5" s="5">
         <v>5</v>
       </c>
-      <c r="I4" s="5">
-        <v>4</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.5833220515289277</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.5833220515289277</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6537852684959868</v>
-      </c>
-      <c r="E5" s="4">
-        <v>79.7732426303855</v>
-      </c>
-      <c r="F5" s="4">
-        <v>84.16853094705448</v>
-      </c>
-      <c r="G5" s="5">
-        <v>9</v>
-      </c>
-      <c r="H5" s="5">
-        <v>9</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
+      <c r="P5" s="4">
+        <v>0.3489997317534833</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07330918253750952</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2903,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2911,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2922,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2964,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,34 +2995,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7424485026194224</v>
+        <v>0.07499470573974223</v>
       </c>
       <c r="C3" s="4">
-        <v>0.514496743591741</v>
+        <v>0.07499470573974223</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5553356016733955</v>
+        <v>0.07084213824503473</v>
       </c>
       <c r="E3" s="4">
-        <v>91.87452758881335</v>
+        <v>95.10204081632654</v>
       </c>
       <c r="F3" s="4">
-        <v>87.67710663683529</v>
+        <v>96.11856823266218</v>
       </c>
       <c r="G3" s="5">
         <v>9</v>
       </c>
       <c r="H3" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2566,34 +3054,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.06192335185464041</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06108960277198868</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06108960277198868</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4262840928775901</v>
+        <v>0.1436969746422076</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4165935790573272</v>
+        <v>0.1436969746422076</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4062940526811636</v>
+        <v>0.1398834402835531</v>
       </c>
       <c r="E4" s="4">
-        <v>92.77399848828419</v>
+        <v>93.86621315192744</v>
       </c>
       <c r="F4" s="4">
-        <v>91.16206810837522</v>
+        <v>94.22073079791204</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2607,34 +3113,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1404388761000001</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06939191604939519</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06939191604939519</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2709351046508747</v>
+        <v>0.4343963474723296</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2709351046508747</v>
+        <v>0.04716358142579224</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2669445140786502</v>
+        <v>0.09912568829013758</v>
       </c>
       <c r="E5" s="4">
-        <v>94.45578231292518</v>
+        <v>89.27815570672709</v>
       </c>
       <c r="F5" s="4">
-        <v>95.60402684563758</v>
+        <v>76.51752423564376</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2648,9 +3172,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4343963474723296</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04716358142579224</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3201,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3209,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3220,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3262,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,132 +3293,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6283777748483159</v>
+        <v>0.5833220515289277</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6048797007231613</v>
+        <v>0.5833220515289277</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7138754339622027</v>
+        <v>0.6537852684959868</v>
       </c>
       <c r="E3" s="4">
-        <v>73.35222978080121</v>
+        <v>79.7732426303855</v>
       </c>
       <c r="F3" s="4">
-        <v>65.75441213024972</v>
+        <v>84.16853094705448</v>
       </c>
       <c r="G3" s="5">
         <v>9</v>
       </c>
       <c r="H3" s="5">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.06495793028400361</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.547234312482259</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.547234312482259</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2517285636580494</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2660651667739302</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3010581408788286</v>
+      </c>
+      <c r="E4" s="4">
+        <v>77.79667422524565</v>
+      </c>
+      <c r="F4" s="4">
+        <v>76.1558538404184</v>
+      </c>
+      <c r="G4" s="5">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5">
         <v>5</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.1650168795158564</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1697048344344088</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1844292059777197</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3220436352762117</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.347881024661531</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3781973195366738</v>
+      </c>
+      <c r="E5" s="4">
+        <v>76.20559334845048</v>
+      </c>
+      <c r="F5" s="4">
+        <v>70.09694258016421</v>
+      </c>
+      <c r="G5" s="5">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5">
+        <v>5</v>
+      </c>
+      <c r="I5" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J5" s="5">
         <v>1</v>
       </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
         <v>1</v>
       </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.4800876992800778</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4590380795572027</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.5168361539490888</v>
-      </c>
-      <c r="E4" s="4">
-        <v>75.43461829176115</v>
-      </c>
-      <c r="F4" s="4">
-        <v>75.53069848371882</v>
-      </c>
-      <c r="G4" s="5">
-        <v>9</v>
-      </c>
-      <c r="H4" s="5">
-        <v>8</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.719164725837306</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.719164725837306</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.7894684738886567</v>
-      </c>
-      <c r="E5" s="4">
-        <v>76.34920634920634</v>
-      </c>
-      <c r="F5" s="4">
-        <v>78.31096196868009</v>
-      </c>
-      <c r="G5" s="5">
-        <v>9</v>
-      </c>
-      <c r="H5" s="5">
-        <v>9</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.347881024661531</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1268963137521772</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09916844916670471</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3501,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3509,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3520,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3562,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,34 +3593,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4483790932488863</v>
+        <v>0.2709351046508747</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1783537334740558</v>
+        <v>0.2709351046508747</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2302541174882538</v>
+        <v>0.2669445140786502</v>
       </c>
       <c r="E3" s="4">
-        <v>89.35374149659863</v>
+        <v>94.45578231292518</v>
       </c>
       <c r="F3" s="4">
-        <v>83.21277653492248</v>
+        <v>95.60402684563758</v>
       </c>
       <c r="G3" s="5">
         <v>9</v>
       </c>
       <c r="H3" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2992,34 +3652,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2709351046508747</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.07444896653366066</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.07444896653366066</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2394246010788825</v>
+        <v>0.4262840928775901</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2394246010788825</v>
+        <v>0.4165935790573272</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2331406290805506</v>
+        <v>0.4062940526811636</v>
       </c>
       <c r="E4" s="4">
-        <v>92.56991685563113</v>
+        <v>92.77399848828419</v>
       </c>
       <c r="F4" s="4">
-        <v>94.04175988068606</v>
+        <v>91.16206810837522</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -3033,34 +3711,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4165935790573272</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06133077068673861</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05809528897478522</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1742239657668693</v>
+        <v>0.7424485026194224</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1742239657668693</v>
+        <v>0.514496743591741</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1721044577121206</v>
+        <v>0.5553356016733955</v>
       </c>
       <c r="E5" s="4">
-        <v>93.82086167800453</v>
+        <v>91.87452758881335</v>
       </c>
       <c r="F5" s="4">
-        <v>95.26099925428784</v>
+        <v>87.67710663683529</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -3074,9 +3770,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.514496743591741</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2579659006749392</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04502121247088672</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3801,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.719164725837306</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.719164725837306</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.7894684738886567</v>
+      </c>
+      <c r="E3" s="4">
+        <v>76.34920634920634</v>
+      </c>
+      <c r="F3" s="4">
+        <v>78.31096196868009</v>
+      </c>
+      <c r="G3" s="5">
+        <v>9</v>
+      </c>
+      <c r="H3" s="5">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.2542200157748865</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5779313837401469</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5779313837401469</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4800876992800778</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.4590380795572027</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.5168361539490888</v>
+      </c>
+      <c r="E4" s="4">
+        <v>75.43461829176115</v>
+      </c>
+      <c r="F4" s="4">
+        <v>75.53069848371882</v>
+      </c>
+      <c r="G4" s="5">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5">
+        <v>8</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.4590380795572027</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2014020105729848</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2028964397063733</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.6283777748483159</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.6048797007231613</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.7138754339622027</v>
+      </c>
+      <c r="E5" s="4">
+        <v>73.35222978080121</v>
+      </c>
+      <c r="F5" s="4">
+        <v>65.75441213024972</v>
+      </c>
+      <c r="G5" s="5">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5">
+        <v>5</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.6048797007231613</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1448418904661851</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1084101636441073</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.1742239657668693</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1742239657668693</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1721044577121206</v>
+      </c>
+      <c r="E3" s="4">
+        <v>93.82086167800453</v>
+      </c>
+      <c r="F3" s="4">
+        <v>95.26099925428784</v>
+      </c>
+      <c r="G3" s="5">
+        <v>9</v>
+      </c>
+      <c r="H3" s="5">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.1742239657668693</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04907860228213468</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04907860228213468</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2394246010788825</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2394246010788825</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2331406290805506</v>
+      </c>
+      <c r="E4" s="4">
+        <v>92.56991685563113</v>
+      </c>
+      <c r="F4" s="4">
+        <v>94.04175988068606</v>
+      </c>
+      <c r="G4" s="5">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2394246010788825</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04922342354536394</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04922342354536394</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.4483790932488863</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1783537334740558</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.2302541174882538</v>
+      </c>
+      <c r="E5" s="4">
+        <v>89.35374149659863</v>
+      </c>
+      <c r="F5" s="4">
+        <v>83.21277653492248</v>
+      </c>
+      <c r="G5" s="5">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5">
+        <v>5</v>
+      </c>
+      <c r="I5" s="5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.1783537334740558</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2915050083620925</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.03866336745707145</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>85.18518518518519</v>
+      </c>
+      <c r="C3" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3.703703703703703</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3.703703703703703</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.2593745037457335</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1657201488502257</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.1734788579455357</v>
+      </c>
+      <c r="K3" s="4">
+        <v>85.18518518518515</v>
+      </c>
+      <c r="L3" s="4">
+        <v>83.48537575606825</v>
+      </c>
+      <c r="M3" s="5">
+        <v>27</v>
+      </c>
+      <c r="N3" s="5">
+        <v>163538.1915569305</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.16090296104829</v>
+      </c>
+      <c r="P3" s="5">
+        <v>5085</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>92.5925925925926</v>
+      </c>
+      <c r="C4" s="3">
+        <v>7.407407407407407</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.1787080342757472</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.1526079915074827</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2045139678139552</v>
+      </c>
+      <c r="K4" s="4">
+        <v>92.07608969513731</v>
+      </c>
+      <c r="L4" s="4">
+        <v>91.43383876046084</v>
+      </c>
+      <c r="M4" s="5">
+        <v>27</v>
+      </c>
+      <c r="N4" s="5">
+        <v>172024.8911380768</v>
+      </c>
+      <c r="O4" s="4">
+        <v>60.67897394641157</v>
+      </c>
+      <c r="P4" s="5">
+        <v>2835</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="C5" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.070124045144485</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.06383477596315804</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.07038274535565507</v>
+      </c>
+      <c r="K5" s="4">
+        <v>90.1461325270849</v>
+      </c>
+      <c r="L5" s="4">
+        <v>91.35636755323483</v>
+      </c>
+      <c r="M5" s="5">
+        <v>27</v>
+      </c>
+      <c r="N5" s="5">
+        <v>434059.6508979797</v>
+      </c>
+      <c r="O5" s="4">
+        <v>149.4695767555027</v>
+      </c>
+      <c r="P5" s="5">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="C6" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.1844197452117127</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1171257650184493</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1149128494024931</v>
+      </c>
+      <c r="K6" s="4">
+        <v>90.1171579743008</v>
+      </c>
+      <c r="L6" s="4">
+        <v>88.60924683072218</v>
+      </c>
+      <c r="M6" s="5">
+        <v>27</v>
+      </c>
+      <c r="N6" s="5">
+        <v>269655.4493904114</v>
+      </c>
+      <c r="O6" s="4">
+        <v>81.98706275172131</v>
+      </c>
+      <c r="P6" s="5">
+        <v>3289</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="C7" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.1030466552825997</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.03823121076388721</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.04575977125192891</v>
+      </c>
+      <c r="K7" s="4">
+        <v>91.48904006046858</v>
+      </c>
+      <c r="L7" s="4">
+        <v>92.30797912005828</v>
+      </c>
+      <c r="M7" s="5">
+        <v>27</v>
+      </c>
+      <c r="N7" s="5">
+        <v>777069.5695877075</v>
+      </c>
+      <c r="O7" s="4">
+        <v>271.4179425734221</v>
+      </c>
+      <c r="P7" s="5">
+        <v>2863</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="C8" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.1571385018117656</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1265555920419973</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.144076645861075</v>
+      </c>
+      <c r="K8" s="4">
+        <v>89.45578231292517</v>
+      </c>
+      <c r="L8" s="4">
+        <v>88.39050459855747</v>
+      </c>
+      <c r="M8" s="5">
+        <v>27</v>
+      </c>
+      <c r="N8" s="5">
+        <v>68267.77219772339</v>
+      </c>
+      <c r="O8" s="4">
+        <v>20.83875830211337</v>
+      </c>
+      <c r="P8" s="5">
+        <v>3276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>62.96296296296296</v>
+      </c>
+      <c r="C9" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="D9" s="3">
+        <v>25.92592592592592</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>25.92592592592592</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.403068726004306</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3753572163430201</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.3546230683265819</v>
+      </c>
+      <c r="K9" s="4">
+        <v>85.05416981607465</v>
+      </c>
+      <c r="L9" s="4">
+        <v>75.14251387853245</v>
+      </c>
+      <c r="M9" s="5">
+        <v>27</v>
+      </c>
+      <c r="N9" s="5">
+        <v>154099.0853309631</v>
+      </c>
+      <c r="O9" s="4">
+        <v>31.89136699730198</v>
+      </c>
+      <c r="P9" s="5">
+        <v>4832</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="C10" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1392990281426221</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.08610752828163619</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.08272355544896026</v>
+      </c>
+      <c r="K10" s="4">
+        <v>91.90350214159734</v>
+      </c>
+      <c r="L10" s="4">
+        <v>90.60692683735067</v>
+      </c>
+      <c r="M10" s="5">
+        <v>27</v>
+      </c>
+      <c r="N10" s="5">
+        <v>278386.9826793671</v>
+      </c>
+      <c r="O10" s="4">
+        <v>90.29743194270745</v>
+      </c>
+      <c r="P10" s="5">
+        <v>3083</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>85.18518518518519</v>
+      </c>
+      <c r="C11" s="3">
+        <v>14.81481481481481</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.1892175396185031</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.08951779201207329</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.09374460983921508</v>
+      </c>
+      <c r="K11" s="4">
+        <v>91.13882590073064</v>
+      </c>
+      <c r="L11" s="4">
+        <v>89.29530201342153</v>
+      </c>
+      <c r="M11" s="5">
+        <v>27</v>
+      </c>
+      <c r="N11" s="5">
+        <v>136501.9690990448</v>
+      </c>
+      <c r="O11" s="4">
+        <v>41.80764750353593</v>
+      </c>
+      <c r="P11" s="5">
+        <v>3265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>85.18518518518519</v>
+      </c>
+      <c r="C12" s="3">
+        <v>14.81481481481481</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.1825449788657457</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.09366359809918837</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1053946263239473</v>
+      </c>
+      <c r="K12" s="4">
+        <v>92.16553287981857</v>
+      </c>
+      <c r="L12" s="4">
+        <v>89.9797000579984</v>
+      </c>
+      <c r="M12" s="5">
+        <v>27</v>
+      </c>
+      <c r="N12" s="5">
+        <v>64389.7864818573</v>
+      </c>
+      <c r="O12" s="4">
+        <v>22.17279148824287</v>
+      </c>
+      <c r="P12" s="5">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>81.48148148148148</v>
+      </c>
+      <c r="C13" s="3">
+        <v>18.51851851851852</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.1882926220979045</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.06195399977707382</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.07779130448832505</v>
+      </c>
+      <c r="K13" s="4">
+        <v>92.74880322499361</v>
+      </c>
+      <c r="L13" s="4">
+        <v>88.95227442207016</v>
+      </c>
+      <c r="M13" s="5">
+        <v>27</v>
+      </c>
+      <c r="N13" s="5">
+        <v>228132.1830749512</v>
+      </c>
+      <c r="O13" s="4">
+        <v>73.14273263063519</v>
+      </c>
+      <c r="P13" s="5">
+        <v>3119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>70.37037037037037</v>
+      </c>
+      <c r="C14" s="3">
+        <v>25.92592592592592</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3.703703703703703</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3.703703703703703</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.281278486889615</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.3338472151611818</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.3326057433988307</v>
+      </c>
+      <c r="K14" s="4">
+        <v>77.9251700680272</v>
+      </c>
+      <c r="L14" s="4">
+        <v>76.80710912254486</v>
+      </c>
+      <c r="M14" s="5">
+        <v>27</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1640386.281013489</v>
+      </c>
+      <c r="O14" s="4">
+        <v>382.5527707587427</v>
+      </c>
+      <c r="P14" s="5">
+        <v>4288</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>85.18518518518519</v>
+      </c>
+      <c r="C15" s="3">
+        <v>14.81481481481481</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.1312485459651128</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.06108392545332817</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.07266168248135567</v>
+      </c>
+      <c r="K15" s="4">
+        <v>93.03476946334087</v>
+      </c>
+      <c r="L15" s="4">
+        <v>91.48106719694968</v>
+      </c>
+      <c r="M15" s="5">
+        <v>27</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1027835.741043091</v>
+      </c>
+      <c r="O15" s="4">
+        <v>384.094073633442</v>
+      </c>
+      <c r="P15" s="5">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>81.48148148148148</v>
+      </c>
+      <c r="C16" s="3">
+        <v>14.81481481481481</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3.703703703703703</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>3.703703703703703</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.3080584282597723</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.3348456722514929</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.3932671115905166</v>
+      </c>
+      <c r="K16" s="4">
+        <v>75.04535147392289</v>
+      </c>
+      <c r="L16" s="4">
+        <v>73.19869086088211</v>
+      </c>
+      <c r="M16" s="5">
+        <v>27</v>
+      </c>
+      <c r="N16" s="5">
+        <v>442480.5476665497</v>
+      </c>
+      <c r="O16" s="4">
+        <v>97.39831557705254</v>
+      </c>
+      <c r="P16" s="5">
+        <v>4543</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>85.18518518518519</v>
+      </c>
+      <c r="C17" s="3">
+        <v>14.81481481481481</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.129935678063197</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.04687108998838457</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.06665464732281746</v>
+      </c>
+      <c r="K17" s="4">
+        <v>91.91484001007808</v>
+      </c>
+      <c r="L17" s="4">
+        <v>90.8385118899653</v>
+      </c>
+      <c r="M17" s="5">
+        <v>27</v>
+      </c>
+      <c r="N17" s="5">
+        <v>334808.988571167</v>
+      </c>
+      <c r="O17" s="4">
+        <v>109.9175930962465</v>
+      </c>
+      <c r="P17" s="5">
+        <v>3046</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3206,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -3847,9 +6019,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>23</v>
+      </c>
+      <c r="C3" s="5">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>25</v>
+      </c>
+      <c r="C4" s="5">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>24</v>
+      </c>
+      <c r="C5" s="5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>24</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>24</v>
+      </c>
+      <c r="C7" s="5">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>24</v>
+      </c>
+      <c r="C8" s="5">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>17</v>
+      </c>
+      <c r="C9" s="5">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5">
+        <v>7</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>7</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>6</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>24</v>
+      </c>
+      <c r="C10" s="5">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>23</v>
+      </c>
+      <c r="C11" s="5">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>23</v>
+      </c>
+      <c r="C12" s="5">
+        <v>4</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>22</v>
+      </c>
+      <c r="C13" s="5">
+        <v>5</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>19</v>
+      </c>
+      <c r="C14" s="5">
+        <v>7</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>1</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>23</v>
+      </c>
+      <c r="C15" s="5">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>22</v>
+      </c>
+      <c r="C16" s="5">
+        <v>4</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>1</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>23</v>
+      </c>
+      <c r="C17" s="5">
+        <v>4</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6787,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6829,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,40 +6860,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4387749014730641</v>
+        <v>0.257354401910119</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5813445619327581</v>
+        <v>0.257354401910119</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5508862364562472</v>
+        <v>0.2593764033885261</v>
       </c>
       <c r="E3" s="4">
-        <v>82.77777777777779</v>
+        <v>86.5419501133787</v>
       </c>
       <c r="F3" s="4">
-        <v>75.71091225453775</v>
+        <v>87.27069351230429</v>
       </c>
       <c r="G3" s="5">
         <v>9</v>
       </c>
       <c r="H3" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -3960,10 +6919,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1367543077838668</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1813797864746375</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1813797864746375</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.1507049326944967</v>
@@ -4001,40 +6978,58 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.003846325926367121</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1485680849576261</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1485680849576261</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.257354401910119</v>
+        <v>0.4387749014730641</v>
       </c>
       <c r="C5" s="4">
-        <v>0.257354401910119</v>
+        <v>0.5813445619327581</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2593764033885261</v>
+        <v>0.5508862364562472</v>
       </c>
       <c r="E5" s="4">
-        <v>86.5419501133787</v>
+        <v>82.77777777777779</v>
       </c>
       <c r="F5" s="4">
-        <v>87.27069351230429</v>
+        <v>75.71091225453775</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -4042,9 +7037,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.5813445619327581</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4481756398049368</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1684065161329636</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7068,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7087,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7129,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,37 +7160,55 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>3.965438474708675</v>
+        <v>0.3171722639849072</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.3171722639849072</v>
       </c>
       <c r="D3" s="4">
-        <v>4.083561211321631</v>
+        <v>0.2992017549856125</v>
       </c>
       <c r="E3" s="4">
-        <v>90.17006802721089</v>
+        <v>93.32199546485262</v>
       </c>
       <c r="F3" s="4">
-        <v>86.58960974397169</v>
+        <v>95.04101416853095</v>
       </c>
       <c r="G3" s="5">
         <v>9</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -4171,12 +7217,30 @@
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.2847708665369864</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1490468216323035</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1490468216323035</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3158645820136157</v>
@@ -4214,37 +7278,53 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.3016622845852213</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1482744239107149</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1482744239107149</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3171722639849072</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3171722639849072</v>
-      </c>
+        <v>3.965438474708675</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.2992017549856125</v>
+        <v>4.083561211321631</v>
       </c>
       <c r="E5" s="4">
-        <v>93.32199546485262</v>
+        <v>90.17006802721089</v>
       </c>
       <c r="F5" s="4">
-        <v>95.04101416853095</v>
+        <v>86.58960974397169</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -4253,11 +7333,29 @@
         <v>0</v>
       </c>
       <c r="M5" s="5">
+        <v>7</v>
+      </c>
+      <c r="N5" s="4">
+        <v>3.853225459402219</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2388028572842231</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1627583682571287</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7366,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7385,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7427,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,34 +7458,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1012242032396165</v>
+        <v>0.1475661708541464</v>
       </c>
       <c r="C3" s="4">
-        <v>0.08173752005198291</v>
+        <v>0.1475661708541464</v>
       </c>
       <c r="D3" s="4">
-        <v>0.08227857071616047</v>
+        <v>0.1475166691966605</v>
       </c>
       <c r="E3" s="4">
-        <v>88.78306878306877</v>
+        <v>91.17913832199547</v>
       </c>
       <c r="F3" s="4">
-        <v>87.33905045985523</v>
+        <v>93.9634601043997</v>
       </c>
       <c r="G3" s="5">
         <v>9</v>
       </c>
       <c r="H3" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -4386,10 +7517,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1475661708541464</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0670678767589848</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0670678767589848</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.06861301178885368</v>
@@ -4427,34 +7576,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.0308017119292256</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.0587224801910828</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0587224801910828</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1475661708541464</v>
+        <v>0.1012242032396165</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1475661708541464</v>
+        <v>0.08173752005198291</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1475166691966605</v>
+        <v>0.08227857071616047</v>
       </c>
       <c r="E5" s="4">
-        <v>91.17913832199547</v>
+        <v>88.78306878306877</v>
       </c>
       <c r="F5" s="4">
-        <v>93.9634601043997</v>
+        <v>87.33905045985523</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -4468,9 +7635,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.05927811305934938</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.0845817784833874</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06665356842753074</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7666,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7685,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7727,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,34 +7758,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3606443775593486</v>
+        <v>0.1314369328006882</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3591615459202255</v>
+        <v>0.1314369328006882</v>
       </c>
       <c r="D3" s="4">
-        <v>0.321257329146609</v>
+        <v>0.163861104590372</v>
       </c>
       <c r="E3" s="4">
-        <v>88.37112622826912</v>
+        <v>91.53817082388511</v>
       </c>
       <c r="F3" s="4">
-        <v>82.65846383295801</v>
+        <v>92.56897837434748</v>
       </c>
       <c r="G3" s="5">
         <v>9</v>
       </c>
       <c r="H3" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -4599,10 +7817,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1014666626558286</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1345176354166647</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1345176354166647</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.1145486218630051</v>
@@ -4640,34 +7876,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.06096026478779019</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1099295309953774</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1099295309953774</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1314369328006882</v>
+        <v>0.3606443775593486</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1314369328006882</v>
+        <v>0.3591615459202255</v>
       </c>
       <c r="D5" s="4">
-        <v>0.163861104590372</v>
+        <v>0.321257329146609</v>
       </c>
       <c r="E5" s="4">
-        <v>91.53817082388511</v>
+        <v>88.37112622826912</v>
       </c>
       <c r="F5" s="4">
-        <v>92.56897837434748</v>
+        <v>82.65846383295801</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -4681,9 +7935,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3591615459202255</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.308812069223096</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1018323104557339</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7966,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7985,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8027,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,34 +8058,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2314550976382179</v>
+        <v>0.06080848239338997</v>
       </c>
       <c r="C3" s="4">
-        <v>0.0609550170271973</v>
+        <v>0.06080848239338997</v>
       </c>
       <c r="D3" s="4">
-        <v>0.07286925511949802</v>
+        <v>0.05787540405137608</v>
       </c>
       <c r="E3" s="4">
-        <v>89.84126984126986</v>
+        <v>92.66439909297053</v>
       </c>
       <c r="F3" s="4">
-        <v>86.93512304250279</v>
+        <v>95.19388516032811</v>
       </c>
       <c r="G3" s="5">
         <v>9</v>
       </c>
       <c r="H3" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -4812,10 +8117,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.04307322339492556</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04393680353393988</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04393680353393988</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.07623121627266174</v>
@@ -4853,34 +8176,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.07623121627266174</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.03218249819059829</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03218249819059829</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.06080848239338997</v>
+        <v>0.2314550976382179</v>
       </c>
       <c r="C5" s="4">
-        <v>0.06080848239338997</v>
+        <v>0.0609550170271973</v>
       </c>
       <c r="D5" s="4">
-        <v>0.05787540405137608</v>
+        <v>0.07286925511949802</v>
       </c>
       <c r="E5" s="4">
-        <v>92.66439909297053</v>
+        <v>89.84126984126986</v>
       </c>
       <c r="F5" s="4">
-        <v>95.19388516032811</v>
+        <v>86.93512304250279</v>
       </c>
       <c r="G5" s="5">
         <v>9</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -4894,9 +8235,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.04911495257204024</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2330206641232609</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.03874589046874159</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8266,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.2869011269167672</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3958076271642561</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4099148036313388</v>
-      </c>
-      <c r="E3" s="4">
-        <v>87.65306122448979</v>
-      </c>
-      <c r="F3" s="4">
-        <v>80.99179716629301</v>
-      </c>
-      <c r="G3" s="5">
-        <v>9</v>
-      </c>
-      <c r="H3" s="5">
-        <v>6</v>
-      </c>
-      <c r="I3" s="5">
-        <v>3</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.1045662778540031</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1045662778540031</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.110195973831047</v>
-      </c>
-      <c r="E4" s="4">
-        <v>89.96598639455783</v>
-      </c>
-      <c r="F4" s="4">
-        <v>91.24161073825503</v>
-      </c>
-      <c r="G4" s="5">
-        <v>9</v>
-      </c>
-      <c r="H4" s="5">
-        <v>9</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.1268912376074073</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1268912376074073</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1340499779393566</v>
-      </c>
-      <c r="E5" s="4">
-        <v>90.74829931972791</v>
-      </c>
-      <c r="F5" s="4">
-        <v>92.93810589112603</v>
-      </c>
-      <c r="G5" s="5">
-        <v>9</v>
-      </c>
-      <c r="H5" s="5">
-        <v>9</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.6935340088896536</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.8824905512677219</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.7020366219949842</v>
-      </c>
-      <c r="E3" s="4">
-        <v>83.22373393801965</v>
-      </c>
-      <c r="F3" s="4">
-        <v>69.51528709917886</v>
-      </c>
-      <c r="G3" s="5">
-        <v>9</v>
-      </c>
-      <c r="H3" s="5">
-        <v>4</v>
-      </c>
-      <c r="I3" s="5">
-        <v>3</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.544133008611987</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4781785377112686</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4465272941050102</v>
-      </c>
-      <c r="E4" s="4">
-        <v>86.21315192743772</v>
-      </c>
-      <c r="F4" s="4">
-        <v>78.85657469549918</v>
-      </c>
-      <c r="G4" s="5">
-        <v>9</v>
-      </c>
-      <c r="H4" s="5">
-        <v>7</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.8427295224241662</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.8438506978495089</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.8353702296520851</v>
-      </c>
-      <c r="E5" s="4">
-        <v>85.72562358276656</v>
-      </c>
-      <c r="F5" s="4">
-        <v>77.05567984091236</v>
-      </c>
-      <c r="G5" s="5">
-        <v>9</v>
-      </c>
-      <c r="H5" s="5">
-        <v>6</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>3</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>3</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/StricklerSystematic2019.xlsx
+++ b/public/downloads/StricklerSystematic2019.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.02767693321305506</v>
+        <v>0.02840231978484553</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1385027081976591</v>
+        <v>0.12373542429798</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1385027081976591</v>
+        <v>0.12373542429798</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.02866245880255727</v>
+        <v>0.06153135498743723</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.09009580248066275</v>
+        <v>0.08221921913786881</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09009580248066275</v>
+        <v>0.08221921913786881</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -1675,13 +1675,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3958076271642561</v>
+        <v>0.3956301310058077</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2428169947569749</v>
+        <v>0.2427578293708255</v>
       </c>
       <c r="Q5" s="4">
         <v>0.1633246021505066</v>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.8438506978495089</v>
+        <v>0.9363217534484818</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2764918751996516</v>
+        <v>0.2488217021527722</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2157978903038168</v>
+        <v>0.1897044733333265</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -1916,16 +1916,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4768238995770194</v>
+        <v>0.5840409665301536</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.239180293923613</v>
+        <v>0.1906095473871498</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2223318758482218</v>
+        <v>0.1905172208593789</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -2155,16 +2155,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.0763233270868966</v>
+        <v>0.1169049345148903</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1180687671584029</v>
+        <v>0.1052677554911675</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1180687671584029</v>
+        <v>0.1052677554911675</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -2214,16 +2214,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.02203195490626738</v>
+        <v>0.008557591324972691</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.07152171148669884</v>
+        <v>0.0700245599776661</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07152171148669884</v>
+        <v>0.0700245599776661</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -2273,16 +2273,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1172556783613998</v>
+        <v>0.09790894663837157</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2283066057827644</v>
+        <v>0.2189679264632489</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06004439515889202</v>
+        <v>0.05570974204113277</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -2455,16 +2455,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2896281417580692</v>
+        <v>0.3304033486938351</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08694453914351589</v>
+        <v>0.07991753049479182</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08694453914351589</v>
+        <v>0.07991753049479182</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -2514,16 +2514,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1070899418185655</v>
+        <v>0.1663336126172226</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.08057975965470526</v>
+        <v>0.07399712956596557</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08057975965470526</v>
+        <v>0.07399712956596557</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -2573,16 +2573,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.343313317654804</v>
+        <v>0.3899151223266699</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4001283200572882</v>
+        <v>0.4156622549479102</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.110238105418739</v>
+        <v>0.1009177444843658</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -2755,16 +2755,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.05891737040932791</v>
+        <v>0.1146628889770227</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1246498966145787</v>
+        <v>0.1087332020572881</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1246498966145787</v>
+        <v>0.1087332020572881</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -2814,16 +2814,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.05876249890951613</v>
+        <v>-0.04683740948246395</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.07398530822917514</v>
+        <v>0.07138077750000901</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07398530822917514</v>
+        <v>0.07138077750000901</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -2873,16 +2873,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.01208507070847418</v>
+        <v>-0.02821434277097978</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3489997317534833</v>
+        <v>0.3400390250520913</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07330918253750952</v>
+        <v>0.07008332812500839</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -3055,16 +3055,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.06192335185464041</v>
+        <v>0.05670657745361041</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06108960277198868</v>
+        <v>0.06050996117187424</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06108960277198868</v>
+        <v>0.06050996117187424</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -3114,16 +3114,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1404388761000001</v>
+        <v>-0.1515945524975564</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06939191604939519</v>
+        <v>0.06815239644966671</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06939191604939519</v>
+        <v>0.06815239644966671</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -3353,16 +3353,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.06495793028400361</v>
+        <v>0.3654178976157958</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.547234312482259</v>
+        <v>0.420500757322603</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.547234312482259</v>
+        <v>0.420500757322603</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -3412,16 +3412,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1650168795158564</v>
+        <v>0.278448382335057</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1697048344344088</v>
+        <v>0.157800232785591</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1844292059777197</v>
+        <v>0.1617429054138796</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -3471,16 +3471,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.347881024661531</v>
+        <v>0.3660500981387784</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1268963137521772</v>
+        <v>0.1289150996940936</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09916844916670471</v>
+        <v>0.09553463447125524</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -3653,16 +3653,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2709351046508747</v>
+        <v>-0.2898956504134844</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.07444896653366066</v>
+        <v>0.07234223922670403</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07444896653366066</v>
+        <v>0.07234223922670403</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -3712,16 +3712,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4165935790573272</v>
+        <v>-0.3896152647574098</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06133077068673861</v>
+        <v>0.06392912785437746</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.05809528897478522</v>
+        <v>0.05764615150088925</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
@@ -3771,13 +3771,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.514496743591741</v>
+        <v>-0.5018646331958081</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2579659006749392</v>
+        <v>0.2621766041402501</v>
       </c>
       <c r="Q5" s="4">
         <v>0.04502121247088672</v>
@@ -3953,16 +3953,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2542200157748865</v>
+        <v>0.5951976840286441</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5779313837401469</v>
+        <v>0.3964353216674965</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5779313837401469</v>
+        <v>0.3964353216674965</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -4012,16 +4012,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4590380795572027</v>
+        <v>0.5829363659144828</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2014020105729848</v>
+        <v>0.1498849308752626</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2028964397063733</v>
+        <v>0.1604270108410959</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
@@ -4071,16 +4071,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.6048797007231613</v>
+        <v>0.6469202973422696</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1448418904661851</v>
+        <v>0.140170713064062</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1084101636441073</v>
+        <v>0.1000020443202857</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -4253,16 +4253,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1742239657668693</v>
+        <v>-0.1621766389274448</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.04907860228213468</v>
+        <v>0.04774001041108752</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04907860228213468</v>
+        <v>0.04774001041108752</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -4312,16 +4312,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2394246010788825</v>
+        <v>-0.22190107682502</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.04922342354536394</v>
+        <v>0.04639365964489528</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04922342354536394</v>
+        <v>0.04639365964489528</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -4371,16 +4371,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1783537334740558</v>
+        <v>-0.1940378321984753</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2915050083620925</v>
+        <v>0.2827916201818594</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.03866336745707145</v>
+        <v>0.03552654771218755</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -4517,13 +4517,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.2593745037457335</v>
+        <v>0.2466833946896932</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1657201488502257</v>
+        <v>0.1363674743775752</v>
       </c>
       <c r="J3" s="4">
-        <v>0.1734788579455357</v>
+        <v>0.1582625106391502</v>
       </c>
       <c r="K3" s="4">
         <v>85.18518518518515</v>
@@ -4567,13 +4567,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.1787080342757472</v>
+        <v>0.1581754422628234</v>
       </c>
       <c r="I4" s="4">
-        <v>0.1526079915074827</v>
+        <v>0.1357270104254894</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2045139678139552</v>
+        <v>0.1951932171289952</v>
       </c>
       <c r="K4" s="4">
         <v>92.07608969513731</v>
@@ -4617,13 +4617,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.070124045144485</v>
+        <v>0.06919490712957099</v>
       </c>
       <c r="I5" s="4">
-        <v>0.06383477596315804</v>
+        <v>0.06203318218823028</v>
       </c>
       <c r="J5" s="4">
-        <v>0.07038274535565507</v>
+        <v>0.07045124316962449</v>
       </c>
       <c r="K5" s="4">
         <v>90.1461325270849</v>
@@ -4667,13 +4667,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.1844197452117127</v>
+        <v>0.182211888933745</v>
       </c>
       <c r="I6" s="4">
-        <v>0.1171257650184493</v>
+        <v>0.1121627897070354</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1149128494024931</v>
+        <v>0.1215049973176239</v>
       </c>
       <c r="K6" s="4">
         <v>90.1171579743008</v>
@@ -4717,13 +4717,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.1030466552825997</v>
+        <v>0.1030369433796278</v>
       </c>
       <c r="I7" s="4">
-        <v>0.03823121076388721</v>
+        <v>0.0380029522949196</v>
       </c>
       <c r="J7" s="4">
-        <v>0.04575977125192891</v>
+        <v>0.04536369032118054</v>
       </c>
       <c r="K7" s="4">
         <v>91.48904006046858</v>
@@ -4767,13 +4767,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.1571385018117656</v>
+        <v>0.1495708242688914</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1265555920419973</v>
+        <v>0.1180641418260699</v>
       </c>
       <c r="J8" s="4">
-        <v>0.144076645861075</v>
+        <v>0.1443803093655097</v>
       </c>
       <c r="K8" s="4">
         <v>89.45578231292517</v>
@@ -4817,13 +4817,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.403068726004306</v>
+        <v>0.3776550861431918</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3753572163430201</v>
+        <v>0.3530476230050881</v>
       </c>
       <c r="J9" s="4">
-        <v>0.3546230683265819</v>
+        <v>0.3537332064546585</v>
       </c>
       <c r="K9" s="4">
         <v>85.05416981607465</v>
@@ -4867,13 +4867,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1392990281426221</v>
+        <v>0.1314200806440275</v>
       </c>
       <c r="I10" s="4">
-        <v>0.08610752828163619</v>
+        <v>0.07966205381109577</v>
       </c>
       <c r="J10" s="4">
-        <v>0.08272355544896026</v>
+        <v>0.08050298373354471</v>
       </c>
       <c r="K10" s="4">
         <v>91.90350214159734</v>
@@ -4917,13 +4917,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.1892175396185031</v>
+        <v>0.1898589716695559</v>
       </c>
       <c r="I11" s="4">
-        <v>0.08951779201207329</v>
+        <v>0.08216611578124546</v>
       </c>
       <c r="J11" s="4">
-        <v>0.09374460983921508</v>
+        <v>0.08891197410075072</v>
       </c>
       <c r="K11" s="4">
         <v>91.13882590073064</v>
@@ -4967,13 +4967,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.1825449788657457</v>
+        <v>0.1733843348697961</v>
       </c>
       <c r="I12" s="4">
-        <v>0.09366359809918837</v>
+        <v>0.08571488941916157</v>
       </c>
       <c r="J12" s="4">
-        <v>0.1053946263239473</v>
+        <v>0.1044707697204175</v>
       </c>
       <c r="K12" s="4">
         <v>92.16553287981857</v>
@@ -5017,13 +5017,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.1882926220979045</v>
+        <v>0.1876862350312902</v>
       </c>
       <c r="I13" s="4">
-        <v>0.06195399977707382</v>
+        <v>0.06120979746804716</v>
       </c>
       <c r="J13" s="4">
-        <v>0.07779130448832505</v>
+        <v>0.07801126382152974</v>
       </c>
       <c r="K13" s="4">
         <v>92.74880322499361</v>
@@ -5067,13 +5067,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.281278486889615</v>
+        <v>0.2357386966007625</v>
       </c>
       <c r="I14" s="4">
-        <v>0.3338472151611818</v>
+        <v>0.2668891850173211</v>
       </c>
       <c r="J14" s="4">
-        <v>0.3326057433988307</v>
+        <v>0.2766255209754871</v>
       </c>
       <c r="K14" s="4">
         <v>77.9251700680272</v>
@@ -5117,13 +5117,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.1312485459651128</v>
+        <v>0.1328159904071105</v>
       </c>
       <c r="I15" s="4">
-        <v>0.06108392545332817</v>
+        <v>0.06010333216838133</v>
       </c>
       <c r="J15" s="4">
-        <v>0.07266168248135567</v>
+        <v>0.07254716935361032</v>
       </c>
       <c r="K15" s="4">
         <v>93.03476946334087</v>
@@ -5167,13 +5167,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.3080584282597723</v>
+        <v>0.2288303218689404</v>
       </c>
       <c r="I16" s="4">
-        <v>0.3348456722514929</v>
+        <v>0.2432429183335302</v>
       </c>
       <c r="J16" s="4">
-        <v>0.3932671115905166</v>
+        <v>0.3117588709980979</v>
       </c>
       <c r="K16" s="4">
         <v>75.04535147392289</v>
@@ -5217,13 +5217,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.129935678063197</v>
+        <v>0.1256417634126141</v>
       </c>
       <c r="I17" s="4">
-        <v>0.04687108998838457</v>
+        <v>0.04455807691586013</v>
       </c>
       <c r="J17" s="4">
-        <v>0.06665464732281746</v>
+        <v>0.06576785106165602</v>
       </c>
       <c r="K17" s="4">
         <v>91.91484001007808</v>
@@ -6920,16 +6920,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1367543077838668</v>
+        <v>0.2201316389770227</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1813797864746375</v>
+        <v>0.1452257544575938</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1813797864746375</v>
+        <v>0.1452257544575938</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -6979,16 +6979,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.003846325926367121</v>
+        <v>0.06654275676390853</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1485680849576261</v>
+        <v>0.1246544687631715</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1485680849576261</v>
+        <v>0.1246544687631715</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -7038,16 +7038,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5813445619327581</v>
+        <v>0.6644574540222266</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4481756398049368</v>
+        <v>0.4701699608483144</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1684065161329636</v>
+        <v>0.1415059803394683</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -7220,16 +7220,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2847708665369864</v>
+        <v>0.3745534453124719</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1490468216323035</v>
+        <v>0.1339143596099145</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1490468216323035</v>
+        <v>0.1339143596099145</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -7279,16 +7279,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3016622845852213</v>
+        <v>0.3576234974999579</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1482744239107149</v>
+        <v>0.1238683527775177</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1482744239107149</v>
+        <v>0.1238683527775177</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -7336,16 +7336,16 @@
         <v>7</v>
       </c>
       <c r="N5" s="4">
-        <v>3.853225459402219</v>
+        <v>3.919403188051774</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2388028572842231</v>
+        <v>0.2167436144010379</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1627583682571287</v>
+        <v>0.1533044070214779</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -7518,16 +7518,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1475661708541464</v>
+        <v>-0.1159805894994861</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.0670678767589848</v>
+        <v>0.0635583677195781</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0670678767589848</v>
+        <v>0.0635583677195781</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -7577,16 +7577,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.0308017119292256</v>
+        <v>0.03295139403809344</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.0587224801910828</v>
+        <v>0.05848362662343081</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0587224801910828</v>
+        <v>0.05848362662343081</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -7636,16 +7636,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.05927811305934938</v>
+        <v>-0.04112658886376153</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.0845817784833874</v>
+        <v>0.08554272704570406</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06665356842753074</v>
+        <v>0.06506973723840777</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -7818,16 +7818,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1014666626558286</v>
+        <v>0.03503563424436607</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1345176354166647</v>
+        <v>0.1223601705295134</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1345176354166647</v>
+        <v>0.1223601705295134</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -7877,16 +7877,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.06096026478779019</v>
+        <v>0.05126604129821999</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1099295309953774</v>
+        <v>0.1088523950520918</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1099295309953774</v>
+        <v>0.1088523950520918</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -7936,13 +7936,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3591615459202255</v>
+        <v>0.3789946419098271</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.308812069223096</v>
+        <v>0.3154231012196299</v>
       </c>
       <c r="Q5" s="4">
         <v>0.1018323104557339</v>
@@ -8118,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.04307322339492556</v>
+        <v>-0.04150293182374298</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.04393680353393988</v>
+        <v>0.04376232669269737</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04393680353393988</v>
+        <v>0.04376232669269737</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -8177,16 +8177,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.07623121627266174</v>
+        <v>-0.0723233045886218</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.03218249819059829</v>
+        <v>0.03174828578126052</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.03218249819059829</v>
+        <v>0.03174828578126052</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -8236,13 +8236,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.04911495257204024</v>
+        <v>0.05085361319703452</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2330206641232609</v>
+        <v>0.2336002176649256</v>
       </c>
       <c r="Q5" s="4">
         <v>0.03874589046874159</v>
